--- a/单片机实训系统开发BOM表.xlsx
+++ b/单片机实训系统开发BOM表.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="78">
   <si>
     <t>产品型号：</t>
   </si>
@@ -211,6 +211,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>xxxxxx</t>
     </r>
     <r>
@@ -428,7 +435,7 @@
     <t>电子元器件</t>
   </si>
   <si>
-    <t>按键模块</t>
+    <t>气敏传感器模块</t>
   </si>
   <si>
     <t>套</t>
@@ -437,7 +444,7 @@
     <t>1)</t>
   </si>
   <si>
-    <t>按键模块电路板</t>
+    <t>气敏传感器模块电路板</t>
   </si>
   <si>
     <t>块</t>
@@ -446,73 +453,19 @@
     <t>2)</t>
   </si>
   <si>
-    <t>TTP223触摸开关模块</t>
-  </si>
-  <si>
-    <t>3)</t>
-  </si>
-  <si>
-    <t>TTP223触摸开关模块电路板</t>
-  </si>
-  <si>
-    <t>4)</t>
-  </si>
-  <si>
-    <t>4x4矩阵键盘模块</t>
-  </si>
-  <si>
-    <t>5)</t>
-  </si>
-  <si>
-    <t>4x4矩阵键盘模块电路板</t>
-  </si>
-  <si>
-    <t>6)</t>
-  </si>
-  <si>
-    <t>7)</t>
-  </si>
-  <si>
-    <t>8)</t>
-  </si>
-  <si>
-    <t>9)</t>
-  </si>
-  <si>
-    <t>10)</t>
-  </si>
-  <si>
-    <t>11)</t>
-  </si>
-  <si>
-    <t>12)</t>
+    <t>继电器模块模块</t>
+  </si>
+  <si>
+    <t>继电器模块电路板</t>
+  </si>
+  <si>
+    <t>信号发生器模块模块</t>
+  </si>
+  <si>
+    <t>信号发生器模块电路板</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>13)</t>
-  </si>
-  <si>
-    <t>14)</t>
-  </si>
-  <si>
-    <t>15)</t>
-  </si>
-  <si>
-    <t>16)</t>
-  </si>
-  <si>
-    <t>17)</t>
-  </si>
-  <si>
-    <t>18)</t>
-  </si>
-  <si>
-    <t>19)</t>
-  </si>
-  <si>
-    <t>20)</t>
   </si>
 </sst>
 </file>
@@ -859,6 +812,26 @@
       <charset val="0"/>
     </font>
     <font>
+      <u/>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
@@ -867,28 +840,8 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="14"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1178,9 +1131,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1189,7 +1140,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1495,7 +1448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1598,6 +1551,63 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="52" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="58" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="60" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="58" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="53" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="55" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1785,7 +1795,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1830,7 +1840,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2302,276 +2312,276 @@
   </cols>
   <sheetData>
     <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="118" t="s">
+      <c r="A4" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="118"/>
-      <c r="C4" s="118"/>
-      <c r="D4" s="119" t="s">
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="119"/>
-      <c r="F4" s="119"/>
-      <c r="G4" s="119"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
     </row>
     <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="118"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
     </row>
     <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="120" t="s">
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
     </row>
     <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="118"/>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
+      <c r="A7" s="137"/>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="140"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
     </row>
     <row r="8" customHeight="1" spans="1:9">
-      <c r="D8" s="122"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="122"/>
-      <c r="H8" s="122"/>
-      <c r="I8" s="122"/>
+      <c r="D8" s="141"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="141"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="141"/>
+      <c r="I8" s="141"/>
     </row>
     <row r="9" customHeight="1" spans="1:9">
-      <c r="D9" s="122"/>
-      <c r="E9" s="122"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="122"/>
-      <c r="H9" s="122"/>
-      <c r="I9" s="122"/>
+      <c r="D9" s="141"/>
+      <c r="E9" s="141"/>
+      <c r="F9" s="141"/>
+      <c r="G9" s="141"/>
+      <c r="H9" s="141"/>
+      <c r="I9" s="141"/>
     </row>
     <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="123" t="s">
+      <c r="A13" s="142" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="123"/>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123"/>
+      <c r="B13" s="142"/>
+      <c r="C13" s="142"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="142"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="142"/>
     </row>
     <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="123"/>
-      <c r="B14" s="123"/>
-      <c r="C14" s="123"/>
-      <c r="D14" s="123"/>
-      <c r="E14" s="123"/>
-      <c r="F14" s="123"/>
-      <c r="G14" s="123"/>
-      <c r="H14" s="123"/>
-      <c r="I14" s="123"/>
+      <c r="A14" s="142"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="142"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="142"/>
+      <c r="F14" s="142"/>
+      <c r="G14" s="142"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="142"/>
     </row>
     <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="124" t="s">
+      <c r="A16" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="124"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="124"/>
-      <c r="F16" s="124"/>
-      <c r="G16" s="124"/>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
+      <c r="B16" s="143"/>
+      <c r="C16" s="143"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
     </row>
     <row r="17" customHeight="1" spans="1:10">
-      <c r="A17" s="124"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="124"/>
-      <c r="D17" s="124"/>
-      <c r="E17" s="124"/>
-      <c r="F17" s="124"/>
-      <c r="G17" s="124"/>
-      <c r="H17" s="124"/>
-      <c r="I17" s="124"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="143"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="143"/>
     </row>
     <row r="18" customHeight="1" spans="1:10">
-      <c r="A18" s="124"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="124"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="124"/>
-      <c r="F18" s="124"/>
-      <c r="G18" s="124"/>
-      <c r="H18" s="124"/>
-      <c r="I18" s="124"/>
+      <c r="A18" s="143"/>
+      <c r="B18" s="143"/>
+      <c r="C18" s="143"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="143"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="125" t="s">
+      <c r="A22" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="125"/>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
+      <c r="B22" s="144"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="144"/>
+      <c r="I22" s="144"/>
     </row>
     <row r="23" customHeight="1" spans="1:10">
-      <c r="A23" s="125"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="125"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
+      <c r="A23" s="144"/>
+      <c r="B23" s="144"/>
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="144"/>
+      <c r="I23" s="144"/>
     </row>
     <row r="24" customHeight="1"/>
     <row r="25" customHeight="1" spans="1:10">
-      <c r="A25" s="126" t="s">
+      <c r="A25" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="127"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
+      <c r="B25" s="146"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="146"/>
+      <c r="E25" s="146"/>
+      <c r="F25" s="146"/>
+      <c r="G25" s="146"/>
+      <c r="H25" s="146"/>
+      <c r="I25" s="146"/>
     </row>
     <row r="26" ht="54.75" customHeight="1" spans="1:10">
-      <c r="A26" s="127"/>
-      <c r="B26" s="127"/>
-      <c r="C26" s="127"/>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="127"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="127"/>
+      <c r="A26" s="146"/>
+      <c r="B26" s="146"/>
+      <c r="C26" s="146"/>
+      <c r="D26" s="146"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="146"/>
+      <c r="H26" s="146"/>
+      <c r="I26" s="146"/>
     </row>
     <row r="32" ht="18.75" spans="1:10">
-      <c r="A32" s="128" t="s">
+      <c r="A32" s="147" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="128"/>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="G32" s="128" t="s">
+      <c r="B32" s="147"/>
+      <c r="C32" s="147"/>
+      <c r="D32" s="147"/>
+      <c r="G32" s="147" t="s">
         <v>6</v>
       </c>
-      <c r="H32" s="129"/>
-      <c r="I32" s="129"/>
-      <c r="J32" s="129"/>
+      <c r="H32" s="148"/>
+      <c r="I32" s="148"/>
+      <c r="J32" s="148"/>
     </row>
     <row r="34" ht="18.75" spans="1:10">
-      <c r="A34" s="128" t="s">
+      <c r="A34" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B34" s="129"/>
-      <c r="C34" s="129"/>
-      <c r="D34" s="129"/>
-      <c r="G34" s="128" t="s">
+      <c r="B34" s="148"/>
+      <c r="C34" s="148"/>
+      <c r="D34" s="148"/>
+      <c r="G34" s="147" t="s">
         <v>8</v>
       </c>
-      <c r="H34" s="129"/>
-      <c r="I34" s="129"/>
-      <c r="J34" s="129"/>
+      <c r="H34" s="148"/>
+      <c r="I34" s="148"/>
+      <c r="J34" s="148"/>
     </row>
     <row r="39" customHeight="1" spans="1:10">
-      <c r="A39" s="130"/>
-      <c r="B39" s="131" t="s">
+      <c r="A39" s="149"/>
+      <c r="B39" s="150" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="131"/>
-      <c r="D39" s="131"/>
-      <c r="E39" s="131"/>
-      <c r="F39" s="131"/>
-      <c r="G39" s="131"/>
-      <c r="H39" s="131"/>
-      <c r="I39" s="131"/>
+      <c r="C39" s="150"/>
+      <c r="D39" s="150"/>
+      <c r="E39" s="150"/>
+      <c r="F39" s="150"/>
+      <c r="G39" s="150"/>
+      <c r="H39" s="150"/>
+      <c r="I39" s="150"/>
     </row>
     <row r="40" customHeight="1" spans="1:10">
-      <c r="A40" s="130"/>
-      <c r="B40" s="131"/>
-      <c r="C40" s="131"/>
-      <c r="D40" s="131"/>
-      <c r="E40" s="131"/>
-      <c r="F40" s="131"/>
-      <c r="G40" s="131"/>
-      <c r="H40" s="131"/>
-      <c r="I40" s="131"/>
+      <c r="A40" s="149"/>
+      <c r="B40" s="150"/>
+      <c r="C40" s="150"/>
+      <c r="D40" s="150"/>
+      <c r="E40" s="150"/>
+      <c r="F40" s="150"/>
+      <c r="G40" s="150"/>
+      <c r="H40" s="150"/>
+      <c r="I40" s="150"/>
     </row>
     <row r="41" customHeight="1" spans="1:10">
-      <c r="A41" s="131" t="s">
+      <c r="A41" s="150" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="131"/>
-      <c r="C41" s="131"/>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="131"/>
-      <c r="I41" s="131"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="150"/>
+      <c r="D41" s="150"/>
+      <c r="E41" s="150"/>
+      <c r="F41" s="150"/>
+      <c r="G41" s="150"/>
+      <c r="H41" s="150"/>
+      <c r="I41" s="150"/>
     </row>
     <row r="42" customHeight="1" spans="1:10">
-      <c r="A42" s="131"/>
-      <c r="B42" s="131"/>
-      <c r="C42" s="131"/>
-      <c r="D42" s="131"/>
-      <c r="E42" s="131"/>
-      <c r="F42" s="131"/>
-      <c r="G42" s="131"/>
-      <c r="H42" s="131"/>
-      <c r="I42" s="131"/>
+      <c r="A42" s="150"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+      <c r="I42" s="150"/>
     </row>
     <row r="43" customHeight="1" spans="1:10">
-      <c r="A43" s="132" t="s">
+      <c r="A43" s="151" t="s">
         <v>11</v>
       </c>
-      <c r="B43" s="132"/>
-      <c r="C43" s="132"/>
-      <c r="D43" s="132"/>
-      <c r="E43" s="132"/>
-      <c r="F43" s="132"/>
-      <c r="G43" s="132"/>
-      <c r="H43" s="132"/>
-      <c r="I43" s="132"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="151"/>
+      <c r="D43" s="151"/>
+      <c r="E43" s="151"/>
+      <c r="F43" s="151"/>
+      <c r="G43" s="151"/>
+      <c r="H43" s="151"/>
+      <c r="I43" s="151"/>
     </row>
     <row r="44" customHeight="1" spans="1:10">
-      <c r="A44" s="132"/>
-      <c r="B44" s="132"/>
-      <c r="C44" s="132"/>
-      <c r="D44" s="132"/>
-      <c r="E44" s="132"/>
-      <c r="F44" s="132"/>
-      <c r="G44" s="132"/>
-      <c r="H44" s="132"/>
-      <c r="I44" s="132"/>
+      <c r="A44" s="151"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="151"/>
+      <c r="D44" s="151"/>
+      <c r="E44" s="151"/>
+      <c r="F44" s="151"/>
+      <c r="G44" s="151"/>
+      <c r="H44" s="151"/>
+      <c r="I44" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2618,128 +2628,128 @@
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1" spans="1:10">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-    </row>
-    <row r="2" s="37" customFormat="1" ht="30.75" customHeight="1" spans="1:10">
-      <c r="A2" s="91" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+    </row>
+    <row r="2" s="56" customFormat="1" ht="30.75" customHeight="1" spans="1:10">
+      <c r="A2" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="110" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91" t="s">
+      <c r="C2" s="110"/>
+      <c r="D2" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91" t="s">
+      <c r="E2" s="110"/>
+      <c r="F2" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="108"/>
-    </row>
-    <row r="3" s="87" customFormat="1" ht="29.25" customHeight="1" spans="1:10">
-      <c r="A3" s="91" t="s">
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="127"/>
+    </row>
+    <row r="3" s="106" customFormat="1" ht="29.25" customHeight="1" spans="1:10">
+      <c r="A3" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="92" t="s">
+      <c r="C3" s="111"/>
+      <c r="D3" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="92"/>
-      <c r="F3" s="109" t="s">
+      <c r="E3" s="111"/>
+      <c r="F3" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="110"/>
-    </row>
-    <row r="4" s="87" customFormat="1" ht="24.75" customHeight="1" spans="1:10">
-      <c r="A4" s="106" t="s">
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="129"/>
+    </row>
+    <row r="4" s="106" customFormat="1" ht="24.75" customHeight="1" spans="1:10">
+      <c r="A4" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="106" t="s">
+      <c r="C4" s="125" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106" t="s">
+      <c r="D4" s="125"/>
+      <c r="E4" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="106" t="s">
+      <c r="F4" s="125" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
     </row>
     <row r="5" ht="35.25" customHeight="1" spans="1:10">
-      <c r="A5" s="74"/>
-      <c r="B5" s="111"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="112"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
+      <c r="A5" s="93"/>
+      <c r="B5" s="130"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+      <c r="J5" s="132"/>
     </row>
     <row r="6" ht="35.25" customHeight="1" spans="1:10">
-      <c r="A6" s="74"/>
-      <c r="B6" s="111"/>
-      <c r="C6" s="112"/>
-      <c r="D6" s="112"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="99"/>
+      <c r="A6" s="93"/>
+      <c r="B6" s="130"/>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="118"/>
     </row>
     <row r="7" ht="35.25" customHeight="1" spans="1:10">
-      <c r="A7" s="74"/>
-      <c r="B7" s="111"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="116"/>
-      <c r="H7" s="116"/>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
+      <c r="A7" s="93"/>
+      <c r="B7" s="130"/>
+      <c r="C7" s="131"/>
+      <c r="D7" s="131"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
+      <c r="I7" s="135"/>
+      <c r="J7" s="136"/>
     </row>
     <row r="8" ht="35.25" customHeight="1" spans="1:10">
-      <c r="A8" s="74"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113"/>
-      <c r="I8" s="113"/>
-      <c r="J8" s="113"/>
+      <c r="A8" s="93"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="132"/>
+      <c r="H8" s="132"/>
+      <c r="I8" s="132"/>
+      <c r="J8" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2778,152 +2788,152 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="8.1" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="87" customWidth="1"/>
-    <col min="2" max="2" width="26.2" style="87" customWidth="1"/>
-    <col min="3" max="3" width="24" style="87" customWidth="1"/>
-    <col min="4" max="4" width="5.1" style="87" customWidth="1"/>
-    <col min="5" max="5" width="5" style="87" customWidth="1"/>
-    <col min="6" max="6" width="6.7" style="87" customWidth="1"/>
-    <col min="7" max="7" width="11.2" style="87" customWidth="1"/>
+    <col min="1" max="1" width="5.5" style="106" customWidth="1"/>
+    <col min="2" max="2" width="26.2" style="106" customWidth="1"/>
+    <col min="3" max="3" width="24" style="106" customWidth="1"/>
+    <col min="4" max="4" width="5.1" style="106" customWidth="1"/>
+    <col min="5" max="5" width="5" style="106" customWidth="1"/>
+    <col min="6" max="6" width="6.7" style="106" customWidth="1"/>
+    <col min="7" max="7" width="11.2" style="106" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1" spans="1:7">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="90"/>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-    </row>
-    <row r="2" s="37" customFormat="1" ht="30.75" customHeight="1" spans="1:7">
-      <c r="A2" s="91" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+    </row>
+    <row r="2" s="56" customFormat="1" ht="30.75" customHeight="1" spans="1:7">
+      <c r="A2" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="110" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91" t="s">
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="91"/>
-    </row>
-    <row r="3" s="87" customFormat="1" ht="29.25" customHeight="1" spans="1:7">
-      <c r="A3" s="91" t="s">
+      <c r="G2" s="110"/>
+    </row>
+    <row r="3" s="106" customFormat="1" ht="29.25" customHeight="1" spans="1:7">
+      <c r="A3" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="92" t="s">
+      <c r="C3" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="92"/>
-      <c r="E3" s="92"/>
-      <c r="F3" s="92" t="s">
+      <c r="D3" s="111"/>
+      <c r="E3" s="111"/>
+      <c r="F3" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="92"/>
-    </row>
-    <row r="4" s="88" customFormat="1" ht="24.75" customHeight="1" spans="1:7">
-      <c r="A4" s="74" t="s">
+      <c r="G3" s="111"/>
+    </row>
+    <row r="4" s="107" customFormat="1" ht="24.75" customHeight="1" spans="1:7">
+      <c r="A4" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="74" t="s">
+      <c r="E4" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="74"/>
-    </row>
-    <row r="5" s="88" customFormat="1" ht="13.5" spans="1:7">
-      <c r="A5" s="93"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-    </row>
-    <row r="6" s="88" customFormat="1" ht="13.5" spans="1:7">
-      <c r="A6" s="74"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="99"/>
-    </row>
-    <row r="7" s="88" customFormat="1" ht="13.5" spans="1:7">
-      <c r="A7" s="74"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="95"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="99"/>
+      <c r="G4" s="93"/>
+    </row>
+    <row r="5" s="107" customFormat="1" ht="13.5" spans="1:7">
+      <c r="A5" s="112"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+    </row>
+    <row r="6" s="107" customFormat="1" ht="13.5" spans="1:7">
+      <c r="A6" s="93"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="116"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="118"/>
+    </row>
+    <row r="7" s="107" customFormat="1" ht="13.5" spans="1:7">
+      <c r="A7" s="93"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="116"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="118"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="74"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="98"/>
-      <c r="G8" s="99"/>
+      <c r="A8" s="93"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="118"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="101"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
+      <c r="A9" s="120"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="102"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="105"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
+      <c r="A10" s="121"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="125"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="102"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="104"/>
-      <c r="E11" s="105"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="106"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="102"/>
-      <c r="B12" s="69"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="106"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="124"/>
+      <c r="F12" s="125"/>
+      <c r="G12" s="125"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2958,39 +2968,39 @@
   <sheetFormatPr defaultColWidth="7.9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8.6" style="3" customWidth="1"/>
-    <col min="2" max="2" width="6.1" style="61" customWidth="1"/>
-    <col min="3" max="3" width="19.4" style="62" customWidth="1"/>
-    <col min="4" max="4" width="18.5" style="62" customWidth="1"/>
+    <col min="2" max="2" width="6.1" style="80" customWidth="1"/>
+    <col min="3" max="3" width="19.4" style="81" customWidth="1"/>
+    <col min="4" max="4" width="18.5" style="81" customWidth="1"/>
     <col min="5" max="5" width="6" style="3" customWidth="1"/>
     <col min="6" max="6" width="4.7" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.4" style="3" customWidth="1"/>
-    <col min="8" max="8" width="16.9" style="63" customWidth="1"/>
+    <col min="8" max="8" width="16.9" style="82" customWidth="1"/>
     <col min="9" max="9" width="4.2" style="3" customWidth="1"/>
-    <col min="10" max="10" width="5" style="61" customWidth="1"/>
-    <col min="11" max="11" width="6.9" style="61" customWidth="1"/>
-    <col min="12" max="12" width="9.6" style="61" customWidth="1"/>
-    <col min="13" max="13" width="12.1" style="61" customWidth="1"/>
-    <col min="14" max="16384" width="7.9" style="36"/>
+    <col min="10" max="10" width="5" style="80" customWidth="1"/>
+    <col min="11" max="11" width="6.9" style="80" customWidth="1"/>
+    <col min="12" max="12" width="9.6" style="80" customWidth="1"/>
+    <col min="13" max="13" width="12.1" style="80" customWidth="1"/>
+    <col min="14" max="16384" width="7.9" style="55"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1" spans="1:20">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-    </row>
-    <row r="2" s="37" customFormat="1" ht="30" customHeight="1" spans="1:20">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+    </row>
+    <row r="2" s="56" customFormat="1" ht="30" customHeight="1" spans="1:20">
       <c r="A2" s="10" t="s">
         <v>13</v>
       </c>
@@ -2999,21 +3009,21 @@
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="65" t="s">
+      <c r="E2" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
       <c r="L2" s="10" t="s">
         <v>16</v>
       </c>
       <c r="M2" s="9"/>
     </row>
-    <row r="3" s="37" customFormat="1" ht="30" customHeight="1" spans="1:20">
+    <row r="3" s="56" customFormat="1" ht="30" customHeight="1" spans="1:20">
       <c r="A3" s="10" t="s">
         <v>17</v>
       </c>
@@ -3022,21 +3032,21 @@
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="65" t="s">
+      <c r="E3" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="66" t="s">
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="85" t="s">
         <v>39</v>
       </c>
       <c r="M3" s="9"/>
     </row>
-    <row r="4" s="37" customFormat="1" ht="15" customHeight="1" spans="1:20">
+    <row r="4" s="56" customFormat="1" ht="15" customHeight="1" spans="1:20">
       <c r="A4" s="10" t="s">
         <v>21</v>
       </c>
@@ -3069,7 +3079,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" s="37" customFormat="1" ht="30" customHeight="1" spans="1:20">
+    <row r="5" s="56" customFormat="1" ht="30" customHeight="1" spans="1:20">
       <c r="A5" s="10"/>
       <c r="B5" s="10"/>
       <c r="C5" s="15"/>
@@ -3096,219 +3106,219 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
     </row>
-    <row r="6" s="37" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A6" s="67"/>
+    <row r="6" s="56" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
+      <c r="A6" s="86"/>
       <c r="B6" s="10"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="69"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="67"/>
-    </row>
-    <row r="7" s="37" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A7" s="67"/>
+      <c r="C6" s="87"/>
+      <c r="D6" s="88"/>
+      <c r="E6" s="89"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="89"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="89"/>
+      <c r="K6" s="89"/>
+      <c r="L6" s="89"/>
+      <c r="M6" s="86"/>
+    </row>
+    <row r="7" s="56" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
+      <c r="A7" s="86"/>
       <c r="B7" s="10"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="71"/>
-    </row>
-    <row r="8" s="37" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A8" s="67"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="89"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="89"/>
+      <c r="L7" s="89"/>
+      <c r="M7" s="90"/>
+    </row>
+    <row r="8" s="56" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
+      <c r="A8" s="86"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="72"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="74"/>
-      <c r="K8" s="70"/>
-      <c r="L8" s="70"/>
-      <c r="M8" s="71"/>
-    </row>
-    <row r="9" s="60" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
-      <c r="A9" s="67"/>
+      <c r="C8" s="91"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="92"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="89"/>
+      <c r="L8" s="89"/>
+      <c r="M8" s="90"/>
+    </row>
+    <row r="9" s="79" customFormat="1" ht="20.1" customHeight="1" spans="1:20">
+      <c r="A9" s="86"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="59"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="67"/>
+      <c r="C9" s="91"/>
+      <c r="D9" s="88"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="92"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="89"/>
+      <c r="L9" s="89"/>
+      <c r="M9" s="86"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="D12" s="75"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="78"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="78"/>
-      <c r="M12" s="78"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="79"/>
-      <c r="R12" s="79"/>
-      <c r="S12" s="79"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="95"/>
+      <c r="F12" s="95"/>
+      <c r="G12" s="95"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="95"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="98"/>
+      <c r="O12" s="98"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="D13" s="75"/>
-      <c r="E13" s="76"/>
-      <c r="F13" s="76"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="79"/>
-      <c r="O13" s="79"/>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="79"/>
-      <c r="R13" s="79"/>
-      <c r="S13" s="79"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="95"/>
+      <c r="F13" s="95"/>
+      <c r="G13" s="95"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="98"/>
+      <c r="O13" s="98"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="98"/>
+      <c r="R13" s="98"/>
+      <c r="S13" s="98"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="D14" s="75"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="85"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="86"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="79"/>
-      <c r="S14" s="79"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="102"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="104"/>
+      <c r="N14" s="100"/>
+      <c r="O14" s="105"/>
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="98"/>
+      <c r="S14" s="98"/>
     </row>
     <row r="15" spans="1:20">
-      <c r="C15" s="75"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="76"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="79"/>
-      <c r="S15" s="79"/>
-      <c r="T15" s="79"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="97"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="95"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="97"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="97"/>
+      <c r="Q15" s="97"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="98"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="C16" s="75"/>
-      <c r="D16" s="75"/>
-      <c r="E16" s="76"/>
-      <c r="F16" s="76"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="79"/>
-      <c r="T16" s="79"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
+      <c r="G16" s="95"/>
+      <c r="H16" s="96"/>
+      <c r="I16" s="95"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="98"/>
+      <c r="O16" s="98"/>
+      <c r="P16" s="98"/>
+      <c r="Q16" s="98"/>
+      <c r="R16" s="98"/>
+      <c r="S16" s="98"/>
+      <c r="T16" s="98"/>
     </row>
     <row r="17" spans="3:20">
-      <c r="C17" s="75"/>
-      <c r="D17" s="75"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="76"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="78"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="79"/>
-      <c r="Q17" s="79"/>
-      <c r="R17" s="79"/>
-      <c r="S17" s="79"/>
-      <c r="T17" s="79"/>
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="95"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="95"/>
+      <c r="H17" s="96"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="98"/>
+      <c r="O17" s="98"/>
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
     </row>
     <row r="18" spans="3:20">
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="76"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="76"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
-      <c r="Q18" s="79"/>
-      <c r="R18" s="79"/>
-      <c r="S18" s="79"/>
-      <c r="T18" s="79"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="96"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="98"/>
+      <c r="Q18" s="98"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="98"/>
+      <c r="T18" s="98"/>
     </row>
     <row r="19" spans="3:20">
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="76"/>
-      <c r="F19" s="76"/>
-      <c r="G19" s="76"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="78"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="79"/>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="79"/>
-      <c r="T19" s="79"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
+      <c r="H19" s="96"/>
+      <c r="I19" s="95"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="98"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="98"/>
+      <c r="Q19" s="98"/>
+      <c r="R19" s="98"/>
+      <c r="S19" s="98"/>
+      <c r="T19" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3348,42 +3358,42 @@
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="7.9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.9" style="37" customWidth="1"/>
-    <col min="2" max="2" width="16.7" style="37" customWidth="1"/>
-    <col min="3" max="3" width="19.4" style="37" customWidth="1"/>
-    <col min="4" max="4" width="3.7" style="37" customWidth="1"/>
-    <col min="5" max="5" width="23.6" style="37" customWidth="1"/>
-    <col min="6" max="6" width="3.9" style="37" customWidth="1"/>
-    <col min="7" max="7" width="5.2" style="37" customWidth="1"/>
-    <col min="8" max="8" width="5.7" style="36" customWidth="1"/>
-    <col min="9" max="9" width="7.7" style="36" customWidth="1"/>
-    <col min="10" max="10" width="4.9" style="36" customWidth="1"/>
-    <col min="11" max="11" width="5.7" style="36" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="36" customWidth="1"/>
-    <col min="13" max="13" width="7.5" style="36" customWidth="1"/>
-    <col min="14" max="14" width="12.5" style="36" customWidth="1"/>
-    <col min="15" max="16384" width="7.9" style="36"/>
+    <col min="1" max="1" width="5.9" style="56" customWidth="1"/>
+    <col min="2" max="2" width="16.7" style="56" customWidth="1"/>
+    <col min="3" max="3" width="19.4" style="56" customWidth="1"/>
+    <col min="4" max="4" width="3.7" style="56" customWidth="1"/>
+    <col min="5" max="5" width="23.6" style="56" customWidth="1"/>
+    <col min="6" max="6" width="3.9" style="56" customWidth="1"/>
+    <col min="7" max="7" width="5.2" style="56" customWidth="1"/>
+    <col min="8" max="8" width="5.7" style="55" customWidth="1"/>
+    <col min="9" max="9" width="7.7" style="55" customWidth="1"/>
+    <col min="10" max="10" width="4.9" style="55" customWidth="1"/>
+    <col min="11" max="11" width="5.7" style="55" customWidth="1"/>
+    <col min="12" max="12" width="8.5" style="55" customWidth="1"/>
+    <col min="13" max="13" width="7.5" style="55" customWidth="1"/>
+    <col min="14" max="14" width="12.5" style="55" customWidth="1"/>
+    <col min="15" max="16384" width="7.9" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" s="36" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A1" s="38" t="s">
+    <row r="1" s="55" customFormat="1" ht="18" customHeight="1" spans="1:14">
+      <c r="A1" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-    </row>
-    <row r="2" s="37" customFormat="1" ht="30" customHeight="1" spans="1:14">
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+    </row>
+    <row r="2" s="56" customFormat="1" ht="30" customHeight="1" spans="1:14">
       <c r="A2" s="9" t="s">
         <v>13</v>
       </c>
@@ -3407,7 +3417,7 @@
       </c>
       <c r="N2" s="9"/>
     </row>
-    <row r="3" s="37" customFormat="1" ht="30" customHeight="1" spans="1:14">
+    <row r="3" s="56" customFormat="1" ht="30" customHeight="1" spans="1:14">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -3431,7 +3441,7 @@
       </c>
       <c r="N3" s="9"/>
     </row>
-    <row r="4" s="37" customFormat="1" ht="15" customHeight="1" spans="1:14">
+    <row r="4" s="56" customFormat="1" ht="15" customHeight="1" spans="1:14">
       <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
@@ -3467,10 +3477,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" s="37" customFormat="1" ht="30" customHeight="1" spans="1:14">
+    <row r="5" s="56" customFormat="1" ht="30" customHeight="1" spans="1:14">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
-      <c r="C5" s="39"/>
+      <c r="C5" s="58"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9" t="s">
@@ -3479,7 +3489,7 @@
       <c r="G5" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="59" t="s">
         <v>50</v>
       </c>
       <c r="I5" s="9" t="s">
@@ -3495,82 +3505,82 @@
       <c r="M5" s="9"/>
       <c r="N5" s="9"/>
     </row>
-    <row r="6" s="37" customFormat="1" ht="21.9" customHeight="1" spans="1:14">
-      <c r="A6" s="41" t="s">
+    <row r="6" s="56" customFormat="1" ht="21.9" customHeight="1" spans="1:14">
+      <c r="A6" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="41"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="60"/>
+      <c r="M6" s="60"/>
+      <c r="N6" s="60"/>
     </row>
     <row r="7" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A7" s="42"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="50"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="70"/>
     </row>
     <row r="8" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A8" s="42"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="52"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="70"/>
+      <c r="M8" s="70"/>
+      <c r="N8" s="71"/>
     </row>
     <row r="9" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:14">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
+      <c r="B9" s="72"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72"/>
     </row>
     <row r="10" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A10" s="54"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="48"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="47"/>
+      <c r="A10" s="73"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="75"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="66"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="J10" s="32"/>
@@ -3580,14 +3590,14 @@
       <c r="N10" s="32"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A11" s="54"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="56"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
+      <c r="A11" s="73"/>
+      <c r="B11" s="74"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
@@ -3596,13 +3606,13 @@
       <c r="N11" s="9"/>
     </row>
     <row r="12" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A12" s="54"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="47"/>
+      <c r="A12" s="73"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="66"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32"/>
@@ -3612,13 +3622,13 @@
       <c r="N12" s="32"/>
     </row>
     <row r="13" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A13" s="54"/>
-      <c r="B13" s="48"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="47"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="76"/>
+      <c r="G13" s="66"/>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -3628,14 +3638,14 @@
       <c r="N13" s="32"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:14">
-      <c r="A14" s="54"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
+      <c r="A14" s="73"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
@@ -3644,13 +3654,13 @@
       <c r="N14" s="9"/>
     </row>
     <row r="15" s="6" customFormat="1" spans="1:14">
-      <c r="A15" s="54"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="47"/>
+      <c r="A15" s="73"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="66"/>
       <c r="H15" s="32"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -3660,13 +3670,13 @@
       <c r="N15" s="32"/>
     </row>
     <row r="16" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A16" s="54"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="57"/>
-      <c r="G16" s="47"/>
+      <c r="A16" s="73"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="75"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="66"/>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -3676,13 +3686,13 @@
       <c r="N16" s="32"/>
     </row>
     <row r="17" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A17" s="54"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="57"/>
-      <c r="G17" s="47"/>
+      <c r="A17" s="73"/>
+      <c r="B17" s="74"/>
+      <c r="C17" s="75"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="75"/>
+      <c r="F17" s="76"/>
+      <c r="G17" s="66"/>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -3692,13 +3702,13 @@
       <c r="N17" s="32"/>
     </row>
     <row r="18" s="6" customFormat="1" ht="18" customHeight="1" spans="1:14">
-      <c r="A18" s="54"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="47"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="66"/>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32"/>
@@ -3707,14 +3717,14 @@
       <c r="M18" s="32"/>
       <c r="N18" s="32"/>
     </row>
-    <row r="19" s="36" customFormat="1" spans="1:14">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
+    <row r="19" s="55" customFormat="1" spans="1:14">
+      <c r="A19" s="56"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="56"/>
+      <c r="G19" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4035,11 +4045,11 @@
     </row>
     <row r="12" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
       <c r="A12" s="26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="27"/>
@@ -4060,7 +4070,7 @@
     </row>
     <row r="13" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
       <c r="A13" s="26" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="30"/>
@@ -4100,7 +4110,7 @@
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
@@ -4121,11 +4131,11 @@
     </row>
     <row r="16" s="2" customFormat="1" ht="16" customHeight="1" spans="1:15">
       <c r="A16" s="26" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="27"/>
@@ -4146,7 +4156,7 @@
     </row>
     <row r="17" s="2" customFormat="1" ht="16" customHeight="1" spans="1:18">
       <c r="A17" s="26" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="30"/>
@@ -4164,601 +4174,475 @@
       <c r="O17" s="25"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16" customHeight="1" spans="1:18">
-      <c r="A18" s="33"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="35"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="38"/>
       <c r="O18" s="25"/>
     </row>
     <row r="19" ht="16" customHeight="1" spans="1:18">
-      <c r="A19" s="18">
-        <v>4</v>
-      </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="24">
-        <v>1</v>
-      </c>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
     </row>
     <row r="20" ht="16" customHeight="1" spans="1:18">
-      <c r="A20" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G20" s="28">
-        <v>1</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="17"/>
-      <c r="N20" s="29"/>
+      <c r="A20" s="47"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="50"/>
     </row>
     <row r="21" ht="16" customHeight="1" spans="1:18">
-      <c r="A21" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="29"/>
+      <c r="A21" s="47"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="53"/>
+      <c r="L21" s="53"/>
+      <c r="M21" s="53"/>
+      <c r="N21" s="50"/>
     </row>
     <row r="22" ht="16" customHeight="1" spans="1:18">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="35"/>
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
     </row>
     <row r="23" ht="16" customHeight="1" spans="1:18">
-      <c r="A23" s="18">
-        <v>5</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="24">
-        <v>1</v>
-      </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="46"/>
+      <c r="L23" s="46"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
     </row>
     <row r="24" ht="16" customHeight="1" spans="1:18">
-      <c r="A24" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="28">
-        <v>1</v>
-      </c>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="29"/>
+      <c r="A24" s="47"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="46"/>
+      <c r="M24" s="46"/>
+      <c r="N24" s="50"/>
     </row>
     <row r="25" ht="16" customHeight="1" spans="1:18">
-      <c r="A25" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="29"/>
+      <c r="A25" s="47"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="50"/>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="33"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34"/>
-      <c r="N26" s="35"/>
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="54"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="54"/>
+      <c r="K26" s="54"/>
+      <c r="L26" s="54"/>
+      <c r="M26" s="54"/>
+      <c r="N26" s="54"/>
     </row>
     <row r="27" spans="1:18">
-      <c r="A27" s="18">
-        <v>6</v>
-      </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="24">
-        <v>1</v>
-      </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
     </row>
     <row r="28" spans="1:18">
-      <c r="A28" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="21"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" s="28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="29"/>
+      <c r="A28" s="47"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="50"/>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="29"/>
+      <c r="A29" s="47"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
+      <c r="L29" s="53"/>
+      <c r="M29" s="53"/>
+      <c r="N29" s="50"/>
     </row>
     <row r="30" spans="1:18">
-      <c r="A30" s="33"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="35"/>
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="54"/>
+      <c r="E30" s="54"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="54"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="54"/>
+      <c r="K30" s="54"/>
+      <c r="L30" s="54"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
     </row>
     <row r="31" spans="1:18">
-      <c r="A31" s="18">
-        <v>7</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="24">
-        <v>1</v>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
       <c r="R31" s="7" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="21"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="28">
-        <v>1</v>
-      </c>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="29"/>
+      <c r="A32" s="47"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="50"/>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="29"/>
+      <c r="A33" s="47"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="53"/>
+      <c r="N33" s="50"/>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="33"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="35"/>
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="54"/>
+      <c r="M34" s="54"/>
+      <c r="N34" s="54"/>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="18">
-        <v>8</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="21"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G35" s="24">
-        <v>1</v>
-      </c>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G36" s="28">
-        <v>1</v>
-      </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="17"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="29"/>
+      <c r="A36" s="47"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="50"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
-      <c r="N37" s="29"/>
+      <c r="A37" s="47"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="53"/>
+      <c r="M37" s="53"/>
+      <c r="N37" s="50"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="33"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34"/>
-      <c r="N38" s="35"/>
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="54"/>
+      <c r="G38" s="54"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="54"/>
+      <c r="N38" s="54"/>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="18">
-        <v>9</v>
-      </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D39" s="21"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" s="24">
-        <v>1</v>
-      </c>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-      <c r="K39" s="17"/>
-      <c r="L39" s="17"/>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
     </row>
     <row r="40" spans="1:14">
-      <c r="A40" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="28">
-        <v>1</v>
-      </c>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="29"/>
+      <c r="A40" s="47"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="46"/>
+      <c r="K40" s="46"/>
+      <c r="L40" s="46"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="50"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="24"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32"/>
-      <c r="N41" s="29"/>
+      <c r="A41" s="47"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="52"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="53"/>
+      <c r="N41" s="50"/>
     </row>
     <row r="42" spans="1:14">
-      <c r="A42" s="33"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="35"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="54"/>
+      <c r="G42" s="54"/>
+      <c r="H42" s="54"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="54"/>
+      <c r="L42" s="54"/>
+      <c r="M42" s="54"/>
+      <c r="N42" s="54"/>
     </row>
     <row r="43" spans="1:14">
-      <c r="A43" s="18">
-        <v>10</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="21"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G43" s="24">
-        <v>1</v>
-      </c>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
+      <c r="A43" s="39"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="43"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="46"/>
+      <c r="L43" s="46"/>
+      <c r="M43" s="46"/>
+      <c r="N43" s="46"/>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="21"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="G44" s="28">
-        <v>1</v>
-      </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="29"/>
+      <c r="A44" s="47"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="46"/>
+      <c r="L44" s="46"/>
+      <c r="M44" s="46"/>
+      <c r="N44" s="50"/>
     </row>
     <row r="45" spans="1:14">
-      <c r="A45" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="32"/>
-      <c r="N45" s="29"/>
+      <c r="A45" s="47"/>
+      <c r="B45" s="40"/>
+      <c r="C45" s="51"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="53"/>
+      <c r="N45" s="50"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="A46" s="33"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="34"/>
-      <c r="N46" s="35"/>
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="54"/>
+      <c r="I46" s="54"/>
+      <c r="J46" s="54"/>
+      <c r="K46" s="54"/>
+      <c r="L46" s="54"/>
+      <c r="M46" s="54"/>
+      <c r="N46" s="54"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="19">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:L2"/>
@@ -4770,13 +4654,6 @@
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="A14:N14"/>
     <mergeCell ref="A18:N18"/>
-    <mergeCell ref="A22:N22"/>
-    <mergeCell ref="A26:N26"/>
-    <mergeCell ref="A30:N30"/>
-    <mergeCell ref="A34:N34"/>
-    <mergeCell ref="A38:N38"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A46:N46"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:C5"/>
